--- a/mod_project/data_tables/grand_seals.xlsx
+++ b/mod_project/data_tables/grand_seals.xlsx
@@ -1399,7 +1399,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aura: Up to +15% EXP gain when defeating higher-level enemies.</t>
+          <t>Aura: Higher-Level Enemy EXP +50% (Underleveled units earn +50% extra EXP).</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
